--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-13_a3_problem_cozme_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/03_FR3 - Kök Neden ve Yatay Yaygınlaştırma/EKG-KLT-FRM-13_a3_problem_cozme_formu.xlsx
@@ -1023,7 +1023,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-13&amp;C&amp;"Arial,Regular"&amp;11A3 Problem Çözme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02284331d353474f"/>
   <x:tableParts count="1">
@@ -1484,7 +1485,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-13&amp;C&amp;"Arial,Regular"&amp;11A3 Problem Çözme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R948255227677474d"/>
   <x:tableParts count="1">
@@ -1922,7 +1924,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-13&amp;C&amp;"Arial,Regular"&amp;11A3 Problem Çözme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75ab1e21bf9a4715"/>
   <x:tableParts count="1">
@@ -2243,7 +2246,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-13&amp;C&amp;"Arial,Regular"&amp;11A3 Problem Çözme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91af25ccdc9d4161"/>
   <x:tableParts count="1">
@@ -2507,7 +2511,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-13&amp;C&amp;"Arial,Regular"&amp;11A3 Problem Çözme Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85504e48427e420c"/>
   <x:tableParts count="1">
